--- a/settings/data/TID.xlsx
+++ b/settings/data/TID.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Godot\touhou_survivors\settings\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\10709\Desktop\thloo\settings\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8A63FDF-B6AF-4D14-9B1F-A81682B02863}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09CE04BA-E601-4B90-AD3C-20EBC9A4E3BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="1290" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TID" sheetId="1" r:id="rId1"/>
+    <sheet name="TID_UI" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -26,12 +27,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="170">
   <si>
     <t>string</t>
   </si>
@@ -475,6 +479,188 @@
   </si>
   <si>
     <t>stg1after</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ufo_settlement_title</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>飞碟结算</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ufo_settlement_fragments</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ufo_settlement_exp</t>
+  </si>
+  <si>
+    <t>ufo_settlement_mana</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ufo_settlement_score</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ufo_settlement_legacy_red</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ufo_settlement_legacy_green</t>
+  </si>
+  <si>
+    <t>ufo_settlement_legacy_blue</t>
+  </si>
+  <si>
+    <t>ufo_settlement_cp_header</t>
+  </si>
+  <si>
+    <t>ufo_settlement_upgrade_header</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ufo_settlement_legacy_colorful</t>
+  </si>
+  <si>
+    <t>记忆碎片{0}</t>
+  </si>
+  <si>
+    <t>获得经验</t>
+  </si>
+  <si>
+    <t>获得符力</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>解锁羁绊</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得分数</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>升级结晶</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>免费符卡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>！</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>得分倍率</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> +{0}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>！</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>额外</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>选取机会！</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>ALL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>！</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="Consolas"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">额外选取机会！
+免费符卡！
+得分倍率 +{0}！
+</t>
+    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -482,7 +668,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -509,6 +695,77 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFE394DC"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFE394DC"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFE394DC"/>
+      <name val="Consolas"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFE394DC"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFE394DC"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF82D2CE"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFE394DC"/>
+      <name val="Consolas"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFE394DC"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -532,7 +789,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -547,6 +804,39 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -816,17 +1106,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H93"/>
-  <sheetFormatPr defaultColWidth="15.08984375" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="15.125" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="28.6328125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="7.453125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.6328125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.453125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="90.54296875" style="1" customWidth="1"/>
-    <col min="6" max="8" width="15.08984375" style="1"/>
+    <col min="1" max="1" width="28.625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="7.5" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5" style="2" customWidth="1"/>
+    <col min="5" max="5" width="90.5" style="1" customWidth="1"/>
+    <col min="6" max="8" width="15.125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -849,7 +1139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -872,7 +1162,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
@@ -895,7 +1185,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A4" s="2" t="str">
         <f t="shared" ref="A4:A13" si="0">IF(ISBLANK(D4),B4&amp;"_"&amp;C4,B4&amp;"_"&amp;C4&amp;"_"&amp;D4)</f>
         <v>cp_reimu_marisa</v>
@@ -915,7 +1205,7 @@
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A5" s="2" t="str">
         <f t="shared" si="0"/>
         <v>cp_reimu_sanae</v>
@@ -935,7 +1225,7 @@
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="str">
         <f t="shared" si="0"/>
         <v>cp_reimu_misumaru</v>
@@ -955,7 +1245,7 @@
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="str">
         <f t="shared" si="0"/>
         <v>cp_marisa_alice</v>
@@ -975,7 +1265,7 @@
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="str">
         <f t="shared" si="0"/>
         <v>cp_marisa_patchouli</v>
@@ -995,7 +1285,7 @@
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A9" s="2" t="str">
         <f t="shared" si="0"/>
         <v>cp_alice_patchouli</v>
@@ -1015,7 +1305,7 @@
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A10" s="2" t="str">
         <f t="shared" si="0"/>
         <v>cp_marisa_alice_patchouli</v>
@@ -1032,7 +1322,7 @@
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A11" s="2" t="str">
         <f t="shared" si="0"/>
         <v>cp_marisa_narumi</v>
@@ -1052,7 +1342,7 @@
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A12" s="2" t="str">
         <f t="shared" si="0"/>
         <v>esc_keine_1</v>
@@ -1072,7 +1362,7 @@
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A13" s="2" t="str">
         <f t="shared" si="0"/>
         <v>esc_keine_2</v>
@@ -1092,7 +1382,7 @@
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A14" s="2" t="str">
         <f t="shared" ref="A14:A48" si="1">IF(ISBLANK(D14),B14&amp;"_"&amp;C14,B14&amp;"_"&amp;C14&amp;"_"&amp;D14)</f>
         <v>psv_patchouli</v>
@@ -1109,7 +1399,7 @@
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A15" s="2" t="str">
         <f t="shared" si="1"/>
         <v>psv_saki</v>
@@ -1126,7 +1416,7 @@
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A16" s="2" t="str">
         <f t="shared" si="1"/>
         <v>psv_narumi</v>
@@ -1143,7 +1433,7 @@
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A17" s="2" t="str">
         <f t="shared" si="1"/>
         <v>psv_junko</v>
@@ -1160,7 +1450,7 @@
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A18" s="2" t="str">
         <f t="shared" si="1"/>
         <v>psv_kisumi</v>
@@ -1177,7 +1467,7 @@
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A19" s="2" t="str">
         <f t="shared" si="1"/>
         <v>psv_momoyo</v>
@@ -1194,7 +1484,7 @@
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A20" s="2" t="str">
         <f t="shared" si="1"/>
         <v>psv_patchouli_dsc</v>
@@ -1214,7 +1504,7 @@
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A21" s="2" t="str">
         <f t="shared" si="1"/>
         <v>psv_saki_dsc</v>
@@ -1234,7 +1524,7 @@
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A22" s="2" t="str">
         <f t="shared" si="1"/>
         <v>psv_narumi_dsc</v>
@@ -1254,7 +1544,7 @@
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A23" s="2" t="str">
         <f t="shared" si="1"/>
         <v>psv_junko_dsc</v>
@@ -1274,7 +1564,7 @@
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A24" s="2" t="str">
         <f t="shared" si="1"/>
         <v>psv_kisumi_dsc</v>
@@ -1294,7 +1584,7 @@
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A25" s="2" t="str">
         <f t="shared" si="1"/>
         <v>psv_momoyo_dsc</v>
@@ -1314,7 +1604,7 @@
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A26" s="2" t="str">
         <f t="shared" si="1"/>
         <v>sc_marisa</v>
@@ -1331,7 +1621,7 @@
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A27" s="2" t="str">
         <f t="shared" si="1"/>
         <v>sc_youmu</v>
@@ -1348,7 +1638,7 @@
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A28" s="2" t="str">
         <f t="shared" si="1"/>
         <v>sc_daiyousei_name</v>
@@ -1368,7 +1658,7 @@
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A29" s="2" t="str">
         <f t="shared" si="1"/>
         <v>sc_marisa_name</v>
@@ -1388,7 +1678,7 @@
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A30" s="2" t="str">
         <f t="shared" si="1"/>
         <v>sc_youmu_name</v>
@@ -1408,7 +1698,7 @@
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A31" s="2" t="str">
         <f t="shared" si="1"/>
         <v>sc_marisa_dsc</v>
@@ -1428,7 +1718,7 @@
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A32" s="2" t="str">
         <f t="shared" si="1"/>
         <v>sc_youmu_dsc</v>
@@ -1448,7 +1738,7 @@
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A33" s="2" t="str">
         <f t="shared" si="1"/>
         <v>ski_reimu</v>
@@ -1465,7 +1755,7 @@
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A34" s="2" t="str">
         <f t="shared" si="1"/>
         <v>ski_sanae</v>
@@ -1482,7 +1772,7 @@
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A35" s="2" t="str">
         <f t="shared" si="1"/>
         <v>ski_rumia</v>
@@ -1499,7 +1789,7 @@
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A36" s="2" t="str">
         <f t="shared" si="1"/>
         <v>ski_wriggle</v>
@@ -1516,7 +1806,7 @@
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A37" s="2" t="str">
         <f t="shared" si="1"/>
         <v>ski_alice</v>
@@ -1533,7 +1823,7 @@
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A38" s="2" t="str">
         <f t="shared" si="1"/>
         <v>ski_sekibanki</v>
@@ -1550,7 +1840,7 @@
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A39" s="2" t="str">
         <f t="shared" si="1"/>
         <v>ski_misumaru</v>
@@ -1567,7 +1857,7 @@
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A40" s="2" t="str">
         <f t="shared" si="1"/>
         <v>ski_sakuya</v>
@@ -1584,7 +1874,7 @@
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A41" s="2" t="str">
         <f t="shared" si="1"/>
         <v>ski_reimu_dsc</v>
@@ -1604,7 +1894,7 @@
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A42" s="2" t="str">
         <f t="shared" si="1"/>
         <v>ski_sanae_dsc</v>
@@ -1624,7 +1914,7 @@
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A43" s="2" t="str">
         <f t="shared" si="1"/>
         <v>ski_rumia_dsc</v>
@@ -1644,7 +1934,7 @@
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A44" s="2" t="str">
         <f t="shared" si="1"/>
         <v>ski_wriggle_dsc</v>
@@ -1664,7 +1954,7 @@
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A45" s="2" t="str">
         <f t="shared" si="1"/>
         <v>ski_alice_dsc</v>
@@ -1684,7 +1974,7 @@
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A46" s="2" t="str">
         <f t="shared" si="1"/>
         <v>ski_sekibanki_dsc</v>
@@ -1704,7 +1994,7 @@
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A47" s="2" t="str">
         <f t="shared" si="1"/>
         <v>ski_misumaru_dsc</v>
@@ -1724,7 +2014,7 @@
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A48" s="2" t="str">
         <f t="shared" si="1"/>
         <v>ski_sakuya_dsc</v>
@@ -1744,7 +2034,7 @@
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A49" s="2" t="s">
         <v>84</v>
       </c>
@@ -1758,7 +2048,7 @@
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
     </row>
-    <row r="50" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A50" s="2" t="s">
         <v>86</v>
       </c>
@@ -1773,7 +2063,7 @@
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
     </row>
-    <row r="51" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A51" s="2" t="str">
         <f>IF(ISBLANK(D51),B51&amp;"_"&amp;C51,B51&amp;"_"&amp;C51&amp;"_"&amp;D51)</f>
         <v>ui_upgrade</v>
@@ -1795,7 +2085,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A52" s="2" t="str">
         <f t="shared" ref="A52:A58" si="2">C52&amp;"_"&amp;D52</f>
         <v>damage_addition</v>
@@ -1815,7 +2105,7 @@
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A53" s="2" t="str">
         <f t="shared" si="2"/>
         <v>bullet_speed_addition</v>
@@ -1835,7 +2125,7 @@
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A54" s="2" t="str">
         <f t="shared" si="2"/>
         <v>duration_addition</v>
@@ -1855,7 +2145,7 @@
       <c r="F54" s="2"/>
       <c r="G54" s="2"/>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A55" s="2" t="str">
         <f t="shared" si="2"/>
         <v>range_addition</v>
@@ -1875,7 +2165,7 @@
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A56" s="2" t="str">
         <f t="shared" si="2"/>
         <v>times_addition</v>
@@ -1895,7 +2185,7 @@
       <c r="F56" s="2"/>
       <c r="G56" s="2"/>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A57" s="2" t="str">
         <f t="shared" si="2"/>
         <v>buff_addition</v>
@@ -1915,7 +2205,7 @@
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A58" s="2" t="str">
         <f t="shared" si="2"/>
         <v>cd_reduction</v>
@@ -1935,7 +2225,7 @@
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A59" s="2" t="str">
         <f t="shared" ref="A59:A63" si="3">IF(ISBLANK(D59),B59&amp;"_"&amp;C59,B59&amp;"_"&amp;C59&amp;"_"&amp;D59)</f>
         <v>name_daiyousei</v>
@@ -1947,7 +2237,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A60" s="2" t="str">
         <f t="shared" si="3"/>
         <v>name_keine</v>
@@ -1962,7 +2252,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A61" s="2" t="str">
         <f t="shared" si="3"/>
         <v>title_keine</v>
@@ -1977,7 +2267,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A62" s="2" t="str">
         <f t="shared" si="3"/>
         <v>dialog_stg1before_1</v>
@@ -1995,7 +2285,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A63" s="2" t="str">
         <f t="shared" si="3"/>
         <v>dialog_stg1before_2</v>
@@ -2013,7 +2303,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A64" s="2" t="str">
         <f t="shared" ref="A64:A85" si="4">IF(ISBLANK(D64),B64&amp;"_"&amp;C64,B64&amp;"_"&amp;C64&amp;"_"&amp;D64)</f>
         <v>dialog_stg1before_3</v>
@@ -2031,7 +2321,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A65" s="2" t="str">
         <f t="shared" si="4"/>
         <v>dialog_stg1before_4</v>
@@ -2049,7 +2339,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A66" s="2" t="str">
         <f t="shared" si="4"/>
         <v>dialog_stg1before_5</v>
@@ -2067,7 +2357,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A67" s="2" t="str">
         <f t="shared" si="4"/>
         <v>dialog_stg1before_6</v>
@@ -2085,7 +2375,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A68" s="2" t="str">
         <f t="shared" si="4"/>
         <v>dialog_stg1before_7</v>
@@ -2103,7 +2393,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A69" s="2" t="str">
         <f t="shared" si="4"/>
         <v>dialog_stg1before_8</v>
@@ -2121,7 +2411,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A70" s="2" t="str">
         <f t="shared" si="4"/>
         <v>dialog_stg1before_9</v>
@@ -2139,7 +2429,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A71" s="2" t="str">
         <f t="shared" si="4"/>
         <v>dialog_stg1before_10</v>
@@ -2157,7 +2447,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A72" s="2" t="str">
         <f t="shared" si="4"/>
         <v>dialog_stg1before_11</v>
@@ -2175,7 +2465,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A73" s="2" t="str">
         <f t="shared" si="4"/>
         <v>dialog_stg1before_12</v>
@@ -2193,7 +2483,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A74" s="2" t="str">
         <f t="shared" si="4"/>
         <v>dialog_stg1before_13</v>
@@ -2211,7 +2501,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A75" s="2" t="str">
         <f t="shared" si="4"/>
         <v>dialog_stg1before_14</v>
@@ -2229,7 +2519,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A76" s="2" t="str">
         <f t="shared" si="4"/>
         <v>dialog_stg1before_15</v>
@@ -2247,7 +2537,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A77" s="2" t="str">
         <f t="shared" si="4"/>
         <v>dialog_stg1before_16</v>
@@ -2265,7 +2555,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A78" s="2" t="str">
         <f t="shared" si="4"/>
         <v>dialog_stg1before_17</v>
@@ -2283,7 +2573,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A79" s="2" t="str">
         <f t="shared" si="4"/>
         <v>dialog_stg1before_18</v>
@@ -2301,7 +2591,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A80" s="2" t="str">
         <f t="shared" si="4"/>
         <v>dialog_stg1before_19</v>
@@ -2319,7 +2609,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A81" s="2" t="str">
         <f t="shared" si="4"/>
         <v>dialog_stg1before_20</v>
@@ -2337,7 +2627,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A82" s="2" t="str">
         <f t="shared" si="4"/>
         <v>dialog_stg1before_21</v>
@@ -2355,7 +2645,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A83" s="2" t="str">
         <f t="shared" si="4"/>
         <v>dialog_stg1before_22</v>
@@ -2373,7 +2663,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A84" s="2" t="str">
         <f t="shared" si="4"/>
         <v>dialog_stg1after_1</v>
@@ -2391,7 +2681,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A85" s="2" t="str">
         <f t="shared" si="4"/>
         <v>dialog_stg1after_2</v>
@@ -2409,7 +2699,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A86" s="2" t="str">
         <f t="shared" ref="A86:A93" si="5">IF(ISBLANK(D86),B86&amp;"_"&amp;C86,B86&amp;"_"&amp;C86&amp;"_"&amp;D86)</f>
         <v>dialog_stg1after_3</v>
@@ -2427,7 +2717,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A87" s="2" t="str">
         <f t="shared" si="5"/>
         <v>dialog_stg1after_4</v>
@@ -2445,7 +2735,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A88" s="2" t="str">
         <f t="shared" si="5"/>
         <v>dialog_stg1after_5</v>
@@ -2463,7 +2753,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A89" s="2" t="str">
         <f t="shared" si="5"/>
         <v>dialog_stg1after_6</v>
@@ -2481,7 +2771,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A90" s="2" t="str">
         <f t="shared" si="5"/>
         <v>dialog_stg1after_7</v>
@@ -2499,7 +2789,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A91" s="2" t="str">
         <f t="shared" si="5"/>
         <v>dialog_stg1after_8</v>
@@ -2517,7 +2807,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A92" s="2" t="str">
         <f t="shared" si="5"/>
         <v>dialog_stg1after_9</v>
@@ -2535,7 +2825,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A93" s="2" t="str">
         <f t="shared" si="5"/>
         <v>dialog_stg1after_10</v>
@@ -2561,4 +2851,177 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88C828DF-D447-45B6-9C95-E5E9AEB64236}">
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="26.125" customWidth="1"/>
+    <col min="5" max="5" width="28.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.15">
+      <c r="A4" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A5" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15" x14ac:dyDescent="0.15">
+      <c r="A6" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="A7" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A8" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A9" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A10" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A11" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="16.5" x14ac:dyDescent="0.15">
+      <c r="A12" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15" x14ac:dyDescent="0.15">
+      <c r="A13" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="72" x14ac:dyDescent="0.15">
+      <c r="A14" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>169</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
 </file>